--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.28676457640598</v>
+        <v>6.546599243665971</v>
       </c>
       <c r="D2" t="n">
-        <v>39.35534288842805</v>
+        <v>6.395243219369559</v>
       </c>
       <c r="E2" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F2" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.20842885805327</v>
+        <v>9.133869689433656</v>
       </c>
       <c r="D3" t="n">
-        <v>56.20095207952068</v>
+        <v>9.132654712922109</v>
       </c>
       <c r="E3" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F3" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.38674224191926</v>
+        <v>4.28784561431188</v>
       </c>
       <c r="D4" t="n">
-        <v>26.11222480070341</v>
+        <v>4.243236530114305</v>
       </c>
       <c r="E4" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F4" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.37000963051788</v>
+        <v>5.422626564959156</v>
       </c>
       <c r="D5" t="n">
-        <v>31.97714503514386</v>
+        <v>5.196286068210878</v>
       </c>
       <c r="E5" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F5" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.75931575043504</v>
+        <v>6.135888809445693</v>
       </c>
       <c r="D6" t="n">
-        <v>38.1880294871253</v>
+        <v>6.205554791657861</v>
       </c>
       <c r="E6" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F6" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.26818952582104</v>
+        <v>7.031080797945919</v>
       </c>
       <c r="D7" t="n">
-        <v>44.07669985661821</v>
+        <v>7.16246372670046</v>
       </c>
       <c r="E7" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F7" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.04968406205017</v>
+        <v>7.320573660083153</v>
       </c>
       <c r="D8" t="n">
-        <v>43.96463665824194</v>
+        <v>7.144253456964315</v>
       </c>
       <c r="E8" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F8" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.42234633097175</v>
+        <v>6.731131278782909</v>
       </c>
       <c r="D9" t="n">
-        <v>40.50636875352848</v>
+        <v>6.582284922448378</v>
       </c>
       <c r="E9" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F9" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.79843927493371</v>
+        <v>5.979746382176727</v>
       </c>
       <c r="D10" t="n">
-        <v>36.06585452822451</v>
+        <v>5.860701360836484</v>
       </c>
       <c r="E10" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F10" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.74724568150671</v>
+        <v>7.271427423244841</v>
       </c>
       <c r="D11" t="n">
-        <v>45.99682713675202</v>
+        <v>7.474484409722204</v>
       </c>
       <c r="E11" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F11" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.94767658439593</v>
+        <v>3.728997444964338</v>
       </c>
       <c r="D12" t="n">
-        <v>23.96575772433932</v>
+        <v>3.894435630205139</v>
       </c>
       <c r="E12" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F12" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.68588368662699</v>
+        <v>5.798956099076886</v>
       </c>
       <c r="D13" t="n">
-        <v>35.81817493579637</v>
+        <v>5.82045342706691</v>
       </c>
       <c r="E13" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F13" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.23293100782193</v>
+        <v>7.837851288771065</v>
       </c>
       <c r="D14" t="n">
-        <v>47.99819953444133</v>
+        <v>7.799707424346717</v>
       </c>
       <c r="E14" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F14" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.98220290374793</v>
+        <v>8.122107971859039</v>
       </c>
       <c r="D15" t="n">
-        <v>50.22464184125416</v>
+        <v>8.161504299203802</v>
       </c>
       <c r="E15" t="n">
-        <v>8.63784592673027</v>
+        <v>1.403649963093669</v>
       </c>
       <c r="F15" t="n">
-        <v>8.662416376152541</v>
+        <v>1.407642661124788</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
